--- a/www/download/IND.gdp.s.du.zdW16.xlsx
+++ b/www/download/IND.gdp.s.du.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>71399.911072785</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>70395.0795293189</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>70817.4775402454</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>79593.220002863</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>87410.9796640238</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>98464.4274813803</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>107651.572107012</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>126302.859329431</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>136076.7436179</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>127984.241643722</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>142554.439768415</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>156147.458110068</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>149349.406591591</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>153356.904045205</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154369.356438715</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>28890.406844846</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>28337.2171176753</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28026.0677491708</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>30731.9343049529</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>34080.4811217751</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>36367.7413585168</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38396.1275646076</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>43874.7462022208</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>48767.5350701566</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>43019.409151268</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>47602.5776274168</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>51549.6909667337</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>50093.09789657</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>49574.8381960235</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49804.7645415128</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24477.1224255996</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24230.1895488714</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>23956.2826510716</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25863.4930609535</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>28555.004467801</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30605.166609011</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32773.2228654555</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>37248.3163992203</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>41063.7547227556</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>36669.349360797</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>40676.1629590996</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>44506.7593570651</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>43422.4781554925</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>42902.44863766</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43062.0332928285</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34014.7804219299</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>33104.4673573156</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>33338.5472286799</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36130.4401200167</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>40121.786316609</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>43249.9444007521</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47409.2572961262</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>54415.3996967179</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>62397.1319974398</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>52450.6445279226</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>53850.8325364152</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>55716.5286112393</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>52490.354614151</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>51918.069634084</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54315.5647842911</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>788983.836986034</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>766611.72813318</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>803794.329182758</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>891492.798969579</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1031750.9512521</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1133998.29769516</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1176553.56843378</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1348028.35253228</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1511780.43493736</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1361388.69007389</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1540951.92063785</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1638986.40187177</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>1610260.55645677</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1639032.1464601</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1670289.2121154</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>105816.693355848</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>104388.134171261</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>106950.002478152</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>117090.8379653</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>131274.275192159</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>143187.295763983</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>152937.49380492</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>174108.229794631</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>193638.823410441</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>168925.056499943</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>191415.039786693</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>205746.912019247</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>207728.527223698</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>206532.373880188</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216678.06341098</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.083</t>
+          <t>9024730.33983812</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8.028</t>
+          <t>8916639.80458001</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.209</t>
+          <t>9130313.74480771</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8.803</t>
+          <t>9793974.89406727</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9.754</t>
+          <t>10816207.6707489</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10.459</t>
+          <t>11667836.1960883</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.458</t>
+          <t>12783724.776663</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13.214</t>
+          <t>14649704.4038912</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>14.861</t>
+          <t>16554806.6059185</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>13.669</t>
+          <t>15291298.6472632</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>15.103</t>
+          <t>16850404.1337438</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>17.402</t>
+          <t>19493552.0467102</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17.056</t>
+          <t>19153069.438815</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>16.835</t>
+          <t>18812379.3794457</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>18.512</t>
+          <t>18511590.9689812</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2018.80023640645</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2014.87376701698</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2030.20474911183</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2454.95428840949</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2698.5255348534</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2953.01524267557</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3123.38577953369</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3617.79578942302</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3996.96978201756</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3646.5275952611</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3852.28427082189</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3912.65563408814</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3566.77885519289</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3198.64884576929</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3062.13968327369</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47315.1564714315</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>44025.0245066054</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>44024.3367362038</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>46797.2062992582</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>52762.6107905344</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>58053.70868539</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>60943.9563313098</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>69279.5220933551</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>76452.5083773456</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>66822.8834372117</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>73826.9816342066</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>79894.9487866291</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>77655.5580700066</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>76735.1311485396</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77449.4554180746</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>247361.574695648</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>239446.670663212</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>237798.002828505</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>253914.794053069</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>278496.600497315</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>295148.413767936</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>316548.941107843</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>360314.301079474</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>397185.324811847</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>347083.139567625</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>393251.407974302</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>429784.538602638</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>421920.187512168</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>420171.73828394</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>429135.165117188</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19617.1033215688</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19506.0350545443</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19409.0417755555</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>20631.9884325969</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22424.5104633656</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24326.6925514708</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26207.8642266502</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29305.4508008786</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32010.0570629971</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28083.38467456</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>29848.9111751065</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32042.2385242637</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30737.4453593751</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30660.872593166</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31068.9921134166</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>130945.164304098</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>132597.760427223</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>136305.812740079</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>152384.344562784</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>170576.828658073</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>188763.670540515</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>203146.243100261</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>230272.282659138</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>243260.841061733</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>200527.187831124</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>214184.728541671</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>218057.674806788</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>197863.654782833</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>188251.454925191</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>190419.482316109</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5926.42531597586</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5920.57913017528</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6010.26831942064</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6932.9955499071</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7659.04203571804</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8321.04128653574</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9142.59028817874</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10383.6913407542</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10812.4762464529</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8167.66306440749</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8518.14582765431</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10321.0190514754</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9716.1536300415</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9395.50645245352</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9609.60761755279</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19841.0855385582</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19542.4515200341</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19603.2335713516</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21103.3895119428</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23275.730227902</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25314.0200527725</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27208.6421164298</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>30997.5436880773</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>34333.6964730372</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>29849.0528487318</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32890.1370578396</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>35566.6879649486</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>34662.7665495157</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>33796.2029552796</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33539.5187344932</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>153954.31799153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>151608.992697903</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>149021.582151561</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>161628.935860081</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>181574.27627017</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>196460.585811843</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>206701.457418915</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>237177.970587974</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>261811.870872115</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>234025.681022049</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>257683.604497961</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>276342.779920551</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>268659.538783759</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>264070.305480423</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264778.440260486</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>183064.042541026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>178861.662338107</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>179403.333232821</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>193178.459090107</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>211964.137371633</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>234203.764136763</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>248814.665274736</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>279245.915568653</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>301655.25045735</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>278502.40692338</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>308117.042989271</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>328688.48179923</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>328101.017182514</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>329371.44690586</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338852.331387414</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>39310.5776668756</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38099.2625555136</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38068.4637934852</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>41484.3743925886</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>44914.4987915923</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>52644.1786420229</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>55240.2343981366</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>62807.0274571155</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>68232.4976004922</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62060.2920553165</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>60951.9943116821</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>58508.1010092605</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>51926.5132940578</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>49759.2379354165</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49401.9044458557</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>47876.9764923913</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>45667.6830591516</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>46133.7369099358</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>48623.4636812567</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>52850.7219368537</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>55525.2909862773</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>58795.6523160967</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>63882.9896939698</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>66371.11543313</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>59247.7188283285</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>58023.4447354343</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>62472.5713232212</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>58201.357338583</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>56154.6615218438</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58975.3750491215</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>932022.803892818</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>965891.020424402</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>1026069.5970181</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>1181166.43072372</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>1316466.00250958</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1291044.73720549</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>1270713.1356954</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1459100.26349266</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1601976.55979036</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1482710.4700402</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1700317.3962957</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1809113.86477504</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>1945812.09317454</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>2156090.93118012</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2.411</t>
+          <t>2410829.80452924</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6889038.32236492</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6964244.1391554</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6.479</t>
+          <t>7206398.21819677</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7.251</t>
+          <t>8067265.70943234</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>9148654.3652937</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8.892</t>
+          <t>9919465.49111821</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.349</t>
+          <t>10431620.8738331</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>10.525</t>
+          <t>11668729.7902376</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11.419</t>
+          <t>12721100.0150265</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>10.411</t>
+          <t>11646611.8249482</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>11.592</t>
+          <t>12932349.5034747</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>12.418</t>
+          <t>13910500.3932749</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>15418153.2664806</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>15.298</t>
+          <t>17095653.6151437</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>18.288</t>
+          <t>18288157.3876224</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15595.0129606973</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15810.8392668149</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15819.7902795098</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17315.4580765308</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19707.5462383362</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22179.7290555287</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24478.4647867592</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28062.6752885328</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>29541.6500548574</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23617.7510384029</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24324.7654502247</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25354.331220415</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24282.4811405441</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25318.9242947058</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26043.6696410938</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>171984.087827667</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>171091.984194925</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>171806.526625482</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>186844.854252322</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>208180.821815825</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>224647.32538176</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>241273.676368657</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>273274.75951927</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>297106.398272406</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>255917.011099666</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>277636.688636051</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>295462.060597285</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>275557.991284925</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>264804.819385511</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>265668.443018526</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>564737.677039735</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>541713.080954832</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>528481.725321724</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>574896.007264643</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>633186.72424133</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>680792.829587982</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>727574.449470578</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>814708.73514212</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>871424.171087175</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>747333.720330914</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>839553.802229634</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>898505.173321078</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>883669.283904739</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>863733.15507555</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>850774.868350627</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>196163.869266876</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>191015.760329437</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>195487.348932132</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>215944.7636625</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>245798.315587704</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>254555.491119863</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>269048.743077432</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>293841.251797522</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>320499.198619366</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>310639.319145762</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>344436.313948149</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>366299.413852554</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>354858.869243238</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>374653.298982124</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>381090.260754691</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15738.8237693022</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14871.7955284747</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15037.5186871061</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>17209.5712617974</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17983.1618856534</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20100.503909227</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21329.9085929038</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23472.7626401161</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24535.8974515378</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19256.1778666217</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20095.1504950655</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21438.4871400205</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21300.7160092585</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>20989.0708991549</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21299.5929451013</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1662.11781703095</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1686.52239839534</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1731.34208741727</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1933.95115068548</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2184.57373317573</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2348.11508655524</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2550.04166754251</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2995.22838554892</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3374.42333231813</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2969.32706119085</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3354.18650317981</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3670.42108204378</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3622.15159289646</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3622.8072700965</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3690.02035412096</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9861.13523923107</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10131.8746422468</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9997.00231969213</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10831.5438603768</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11211.0332429619</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12014.5187554189</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13787.7908335468</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14863.6876774351</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16788.2377643186</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12215.9622520338</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12417.3449013965</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13823.0079030969</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13779.7931207139</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13820.6522766306</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13736.1806043414</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>397521.39490987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>379492.799808828</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>377543.2130058</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>422319.204726435</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>491279.060713646</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>527590.700927729</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>585444.792222928</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>670338.396258121</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>742201.60113159</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>644375.655564617</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>724729.172427482</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>777152.902556674</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>780556.536839848</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>765601.015817773</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>776303.796438713</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1408.22119632289</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1290.35658366885</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1333.76560276466</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1433.59302755624</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1464.08155761504</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1667.24054257074</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1676.39027912909</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1943.63600193352</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2262.68300155032</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2125.73174649449</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2354.54890431421</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2326.60472682856</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2208.72583167067</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2218.25674306779</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2176.87289066355</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>44943.8091890078</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>44870.8786956813</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>45597.1643840377</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>49402.451415091</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>53940.5990178098</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>57837.1908332733</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61325.3615949725</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>70041.0538229191</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>77890.8546174492</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>70783.7860751638</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>77310.3957991133</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>83200.5886141643</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>80414.6647128292</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>79093.4979562173</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78445.6419114016</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>179915.294435074</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>180009.011833402</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>168291.079246152</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>181710.871151615</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>201721.208406041</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>221345.447264302</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>239047.06565729</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>274062.673816051</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>310619.375344495</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>275657.976857742</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>293494.522388104</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>312888.941091295</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>302454.93874374</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>301981.797215097</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>302506.168180992</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>52365.0465021402</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>51551.6721377962</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>51317.8532905595</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>54449.8861638407</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>58421.5547570116</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61614.8622889407</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>64291.4056746602</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>71435.5350398787</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>76294.8368259277</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>67056.995545616</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>72576.9115980994</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>75136.5225262572</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>69509.4365947807</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>67702.965609886</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69003.9463222465</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>149212.261971596</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>146135.595908147</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>124792.035863807</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>140055.924258042</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>146812.567983121</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>157346.59122497</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>162114.594666035</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>182672.760665446</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>196657.822460056</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>172678.864388724</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>191747.328011254</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>204299.285944185</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>150245.901964755</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>147653.379475015</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148270.675510342</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>872753.797465341</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>843909.442360574</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>846103.576225818</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>920347.46252327</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>1012863.53626235</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>1098486.06793073</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1166419.29552415</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1309751.911145</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1299886.64485593</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>1117152.94290614</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1234405.05762769</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.144</t>
+          <t>1281506.69610204</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1277574.17773836</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1209248.95372332</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1169947.00402716</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19004.5638285239</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>18664.5462054871</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17867.2706030202</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>18904.2109587288</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21133.0081709671</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22859.5262694792</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24177.6138013433</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>27385.1332023389</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>31121.496619773</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>26466.7635054693</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29443.4761031798</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>31530.1120684263</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30208.0980567175</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29586.2779476974</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29942.1666012477</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8408.13997004549</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8137.6373325351</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8342.28922575737</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8972.6890428112</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10004.9321306429</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10545.5166961682</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11008.2195053734</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12547.7531018776</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14132.8224753671</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12431.5588620166</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13488.2498779423</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13895.8401743648</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13133.7632186359</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13057.277904618</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13436.8200929977</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36013.6220517813</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>35652.8104655652</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>35548.2700931121</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38110.1468241652</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>42249.2017544349</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>45396.3330003546</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>48214.0870018833</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>55443.3991797459</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61394.8530557094</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>54107.00164344</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>60657.5177218178</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>66204.1612967583</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>64378.1278881126</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>63989.1826808153</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64959.4409399325</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>280384.654912469</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>276323.856550368</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>258843.529136753</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>272125.596363674</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>304635.876844534</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>324456.014866807</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>328363.878084003</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>346413.742660406</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>384860.071058913</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>344545.637602444</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>409842.893727465</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>467441.747108257</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>493956.497134742</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>527715.586224294</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>593164.621506673</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>169110.132286262</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>154342.106649144</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>164734.86547853</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>182381.612173994</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>205664.106879143</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>220004.331446212</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>239708.244365677</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>271446.609487661</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>288868.336056005</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>263273.632033985</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>308311.498269664</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>318562.424625418</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>315631.410782688</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>317522.910665935</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>325383.737309706</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>849544.215841984</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>826357.30071013</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>814189.909328612</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>877187.031439594</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>978586.729084624</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>1073833.28847318</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1165021.8294978</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>1324133.51566718</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1425340.34746237</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1213035.33983782</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1338494.67658668</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1.293</t>
+          <t>1448109.77783564</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>1445105.23553206</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1462947.73309519</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1507400.50281754</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>13565332.8793493</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>12.377</t>
+          <t>13746950.2596408</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>13.104</t>
+          <t>14574481.5025021</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>14.684</t>
+          <t>16336500.0877118</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>16.677</t>
+          <t>18493853.3347124</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18.187</t>
+          <t>20288307.0687976</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>19.799</t>
+          <t>22090966.1454408</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>22.737</t>
+          <t>25208133.8583726</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>25.266</t>
+          <t>28146696.9156493</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>23.288</t>
+          <t>26051794.1105518</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>26.022</t>
+          <t>29031985.0297201</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>28.835</t>
+          <t>32301341.204378</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>29.715</t>
+          <t>33368342.5883974</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>31.171</t>
+          <t>34833233.111117</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>36.382</t>
+          <t>36382245.2205024</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>32.661</t>
+          <t>36464391.5745186</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>36474875.5243052</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>33.986</t>
+          <t>37798471.4616131</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>37.545</t>
+          <t>41770227.9805108</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>42.313</t>
+          <t>46922341.1628257</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>45.644</t>
+          <t>50918440.365171</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>49.148</t>
+          <t>54836542.2885824</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>56.212</t>
+          <t>62319960.7110691</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>62.033</t>
+          <t>69105528.7059354</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>56.604</t>
+          <t>63321172.4464866</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>63.072</t>
+          <t>70366924.1660562</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>69.659</t>
+          <t>78033482.4710755</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>71.423</t>
+          <t>80204851.4982889</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>74.433</t>
+          <t>83177210.8965042</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>86.033</t>
+          <t>86032547.6326592</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16965.549309899</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16124.3645003437</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16262.4965816717</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17510.4605428699</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20179.1973073216</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21669.1125785004</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23080.750933232</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>26071.2244768136</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29486.377370781</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26227.0599775173</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>27791.8209833944</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>28724.9432260028</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>26445.2597072346</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25442.8599107664</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25845.283331421</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32725.2007380877</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>31655.8119619704</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>31323.9849720191</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>34098.8589189727</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38176.3165273641</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>41646.2681981743</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>44811.7864870946</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>50904.8162319131</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>56220.2585407691</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>50881.3925964188</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>56823.368504341</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62158.896492103</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61332.7283842943</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61093.293847904</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62128.6643176508</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16434.624861929</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15952.4399087117</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16065.1181588246</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17297.0793704886</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19384.6748270055</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21262.6115106894</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23174.092427173</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>27218.7391539167</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30593.2201575276</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>27554.4566394261</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30378.7557957818</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33037.1740732228</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32891.9296982112</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>33174.1547151973</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33694.4664302029</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
